--- a/database/flash_2.xlsx
+++ b/database/flash_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\kawkab\backend\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBF569C-BF7F-4627-B45B-BF3385F724DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EACDB9C-8B2E-4459-92C2-48A7EEF62813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="13200" windowHeight="9840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="187">
   <si>
     <t>فرض كفاية</t>
   </si>
@@ -581,138 +581,6 @@
   </si>
   <si>
     <t>e4c5605b-0f62-4162-a4de-720ae3cf11e9</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e10</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e11</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e12</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e13</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e14</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e15</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e16</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e17</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e18</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e19</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e20</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e21</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e22</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e23</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e24</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e25</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e26</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e27</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e28</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e29</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e30</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e31</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e32</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e33</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e34</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e35</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e36</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e37</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e38</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e39</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e40</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e41</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e42</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e43</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e44</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e45</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e46</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e47</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e48</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e49</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e50</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e51</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e52</t>
-  </si>
-  <si>
-    <t>e4c5605b-0f62-4162-a4de-720ae3cf11e53</t>
   </si>
 </sst>
 </file>
@@ -1052,7 +920,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1063,7 +931,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1074,7 +942,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1085,7 +953,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1096,7 +964,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1107,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1118,7 +986,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1129,7 +997,7 @@
         <v>17</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1140,7 +1008,7 @@
         <v>19</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1151,7 +1019,7 @@
         <v>21</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1162,7 +1030,7 @@
         <v>23</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1173,7 +1041,7 @@
         <v>25</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1184,7 +1052,7 @@
         <v>27</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1195,7 +1063,7 @@
         <v>29</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1206,7 +1074,7 @@
         <v>31</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1217,7 +1085,7 @@
         <v>33</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1228,7 +1096,7 @@
         <v>35</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1239,7 +1107,7 @@
         <v>37</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1250,7 +1118,7 @@
         <v>39</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1261,7 +1129,7 @@
         <v>41</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1272,7 +1140,7 @@
         <v>43</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1283,7 +1151,7 @@
         <v>45</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1294,7 +1162,7 @@
         <v>47</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1305,7 +1173,7 @@
         <v>49</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1316,7 +1184,7 @@
         <v>51</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1327,7 +1195,7 @@
         <v>53</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1338,7 +1206,7 @@
         <v>55</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>213</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1349,7 +1217,7 @@
         <v>57</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1360,7 +1228,7 @@
         <v>59</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>215</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1371,7 +1239,7 @@
         <v>61</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>216</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1382,7 +1250,7 @@
         <v>63</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>217</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1393,7 +1261,7 @@
         <v>65</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1404,7 +1272,7 @@
         <v>67</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1415,7 +1283,7 @@
         <v>69</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1426,7 +1294,7 @@
         <v>71</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1437,7 +1305,7 @@
         <v>73</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>222</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1448,7 +1316,7 @@
         <v>75</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1459,7 +1327,7 @@
         <v>77</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>224</v>
+        <v>186</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1470,7 +1338,7 @@
         <v>79</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>225</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1481,7 +1349,7 @@
         <v>81</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>226</v>
+        <v>186</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1492,7 +1360,7 @@
         <v>83</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>227</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1503,7 +1371,7 @@
         <v>85</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>228</v>
+        <v>186</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1514,7 +1382,7 @@
         <v>87</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>229</v>
+        <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1525,7 +1393,7 @@
         <v>89</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>230</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47" spans="1:3">
